--- a/테스트/통합테스트/2026-09-10/2026-09-10/최도훈/테스트시나리오_최도훈.xlsx
+++ b/테스트/통합테스트/2026-09-10/2026-09-10/최도훈/테스트시나리오_최도훈.xlsx
@@ -790,7 +790,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 회차 · 15번 최도훈 — 처방전 · 차상위경감(본인 0% / 공단 100%) · 가상계좌</t>
+          <t>2026-09-10 회차 · 15번 최도훈 — 처방전 · 차상위경감(본인 0% / 공단 100%) · 결제 없음</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>CASE-15 처방전 · 차상위경감 자격(본인 0% / 공단 100%) · 가상계좌</t>
+          <t>CASE-15 처방전 · 차상위경감 자격(본인 0% / 공단 100%) · 결제 안내 없음</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
 송금자명: 최도훈 / 현금영수증: 소득공제 · 010-0000-1003
 건보등록: 신규 등록 진행중 · 2026-09-10 / 재평가: Y · 2028-09-10
 건보위임 시작일: 2026-09-10
-메모: 통합테스트 2026-09-10 · CASE-15 최도훈 · 차상위경감 · 가상계좌</t>
+메모: 통합테스트 2026-09-10 · CASE-15 최도훈 · 차상위경감 · 결제 없음</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
@@ -1790,7 +1790,7 @@
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>담당자: 김선미
-메모: 통합테스트 2026-09-10 · CASE-15 최도훈 · 차상위경감 · 가상계좌</t>
+메모: 통합테스트 2026-09-10 · CASE-15 최도훈 · 차상위경감 · 결제 없음</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -1806,7 +1806,7 @@
       <c r="L7" s="41" t="inlineStr">
         <is>
           <t>① RX-20260911-014 채번
-② 첨부 8건 저장 (처방전 그림은 따로)
+② 첨부 9건 저장 (처방전 그림은 따로)
 ③ 처방전 목록이 「검수 필요 · RX-20260911-014」로 좁혀져 열림</t>
         </is>
       </c>
@@ -2700,7 +2700,7 @@
       <c r="L22" s="30" t="inlineStr">
         <is>
           <t>① 주문 EUD202609110235091
-② 판매주문 S2609110014 · 창고 상태 등록
+② 판매주문 S2609110014 · 창고 상태 확정
 ③ 본인부담금이 0원이라 결제 안내를 보내지 않는다</t>
         </is>
       </c>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="L23" s="35" t="inlineStr">
         <is>
-          <t>판매주문 S2609110014 가 「등록」로 조회된다</t>
+          <t>판매주문 S2609110014 가 「확정」로 조회된다</t>
         </is>
       </c>
       <c r="M23" s="36" t="inlineStr">
